--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845758</v>
+        <v>128845756</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>91953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490634</v>
+        <v>490682</v>
       </c>
       <c r="R2" t="n">
-        <v>7047978</v>
+        <v>7048040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>91948</v>
+        <v>92434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R3" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,45 +877,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R4" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,53 +1592,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845761</v>
+        <v>128845792</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>92778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490666</v>
+        <v>490278</v>
       </c>
       <c r="R11" t="n">
-        <v>7048312</v>
+        <v>7048250</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,32 +1693,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B12" t="n">
-        <v>92773</v>
+        <v>92817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R12" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845762</v>
+        <v>128845791</v>
       </c>
       <c r="B13" t="n">
-        <v>92812</v>
+        <v>92196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490673</v>
+        <v>490641</v>
       </c>
       <c r="R13" t="n">
-        <v>7047987</v>
+        <v>7047962</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,45 +1895,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845791</v>
+        <v>128845761</v>
       </c>
       <c r="B14" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490641</v>
+        <v>490666</v>
       </c>
       <c r="R14" t="n">
-        <v>7047962</v>
+        <v>7048312</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,32 +2105,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845774</v>
+        <v>128845775</v>
       </c>
       <c r="B16" t="n">
-        <v>92191</v>
+        <v>92821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490453</v>
+        <v>490496</v>
       </c>
       <c r="R16" t="n">
-        <v>7048050</v>
+        <v>7048026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,32 +2206,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845775</v>
+        <v>128845774</v>
       </c>
       <c r="B17" t="n">
-        <v>92816</v>
+        <v>92196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490496</v>
+        <v>490453</v>
       </c>
       <c r="R17" t="n">
-        <v>7048026</v>
+        <v>7048050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2310,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B22" t="n">
-        <v>91790</v>
+        <v>57713</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,34 +2730,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R22" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>91795</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2831,42 +2839,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R23" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,32 +2929,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>92818</v>
+        <v>91795</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R24" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,32 +3030,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>91790</v>
+        <v>92823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3065,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R25" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3333,32 +3333,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845765</v>
+        <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>91029</v>
+        <v>91495</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5747</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490278</v>
+        <v>490409</v>
       </c>
       <c r="R28" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,32 +3434,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845753</v>
+        <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>91490</v>
+        <v>91034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5747</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490409</v>
+        <v>490278</v>
       </c>
       <c r="R29" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3647,7 +3647,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845756</v>
+        <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>91953</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490682</v>
+        <v>490634</v>
       </c>
       <c r="R2" t="n">
-        <v>7048040</v>
+        <v>7047978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845754</v>
+        <v>128845756</v>
       </c>
       <c r="B3" t="n">
-        <v>92434</v>
+        <v>91958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490396</v>
+        <v>490682</v>
       </c>
       <c r="R3" t="n">
-        <v>7048167</v>
+        <v>7048040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,53 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845758</v>
+        <v>128845754</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>92439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490634</v>
+        <v>490396</v>
       </c>
       <c r="R4" t="n">
-        <v>7047978</v>
+        <v>7048167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>91500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R7" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B8" t="n">
-        <v>91495</v>
+        <v>92828</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R8" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>91495</v>
+        <v>91500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128845792</v>
       </c>
       <c r="B11" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>128845762</v>
       </c>
       <c r="B12" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,21 +1706,12 @@
       <c r="E12" t="n">
         <v>5449</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1797,7 +1788,7 @@
         <v>128845791</v>
       </c>
       <c r="B13" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,32 +2096,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845775</v>
+        <v>128845774</v>
       </c>
       <c r="B16" t="n">
-        <v>92821</v>
+        <v>92201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2140,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490496</v>
+        <v>490453</v>
       </c>
       <c r="R16" t="n">
-        <v>7048026</v>
+        <v>7048050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,32 +2197,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845774</v>
+        <v>128845775</v>
       </c>
       <c r="B17" t="n">
-        <v>92196</v>
+        <v>92828</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2241,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490453</v>
+        <v>490496</v>
       </c>
       <c r="R17" t="n">
-        <v>7048050</v>
+        <v>7048026</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,7 +2503,7 @@
         <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2822,7 @@
         <v>128845777</v>
       </c>
       <c r="B23" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B24" t="n">
-        <v>91795</v>
+        <v>92830</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R24" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B25" t="n">
-        <v>92823</v>
+        <v>91800</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3065,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R25" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3232,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845770</v>
+        <v>128845753</v>
       </c>
       <c r="B27" t="n">
-        <v>92821</v>
+        <v>91500</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3243,21 +3234,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3267,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490317</v>
+        <v>490409</v>
       </c>
       <c r="R27" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3333,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845753</v>
+        <v>128845770</v>
       </c>
       <c r="B28" t="n">
-        <v>91495</v>
+        <v>92828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3344,21 +3335,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3368,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490409</v>
+        <v>490317</v>
       </c>
       <c r="R28" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,7 +3428,7 @@
         <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92821</v>
+        <v>92828</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845758</v>
+        <v>128845754</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490634</v>
+        <v>490396</v>
       </c>
       <c r="R2" t="n">
-        <v>7047978</v>
+        <v>7048167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -885,45 +877,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B4" t="n">
-        <v>92439</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R4" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>91500</v>
+        <v>92828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R7" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>92828</v>
+        <v>91500</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R8" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845750</v>
+        <v>128845781</v>
       </c>
       <c r="B9" t="n">
-        <v>91500</v>
+        <v>92201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490385</v>
+        <v>490331</v>
       </c>
       <c r="R9" t="n">
-        <v>7048282</v>
+        <v>7048266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845781</v>
+        <v>128845750</v>
       </c>
       <c r="B10" t="n">
-        <v>92201</v>
+        <v>91500</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490331</v>
+        <v>490385</v>
       </c>
       <c r="R10" t="n">
-        <v>7048266</v>
+        <v>7048282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,25 +1693,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845762</v>
+        <v>128845791</v>
       </c>
       <c r="B12" t="n">
-        <v>92823</v>
+        <v>92201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1719,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490673</v>
+        <v>490641</v>
       </c>
       <c r="R12" t="n">
-        <v>7047987</v>
+        <v>7047962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,34 +1794,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845791</v>
+        <v>128845762</v>
       </c>
       <c r="B13" t="n">
-        <v>92201</v>
+        <v>92823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490641</v>
+        <v>490673</v>
       </c>
       <c r="R13" t="n">
-        <v>7047962</v>
+        <v>7047987</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845774</v>
+        <v>128845775</v>
       </c>
       <c r="B16" t="n">
-        <v>92201</v>
+        <v>92828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490453</v>
+        <v>490496</v>
       </c>
       <c r="R16" t="n">
-        <v>7048050</v>
+        <v>7048026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,32 +2197,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845775</v>
+        <v>128845774</v>
       </c>
       <c r="B17" t="n">
-        <v>92828</v>
+        <v>92201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490496</v>
+        <v>490453</v>
       </c>
       <c r="R17" t="n">
-        <v>7048026</v>
+        <v>7048050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>91800</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,42 +2721,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R22" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B23" t="n">
-        <v>91800</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,34 +2822,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R23" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>92830</v>
+        <v>91800</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R24" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>91800</v>
+        <v>92830</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R25" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845753</v>
+        <v>128845780</v>
       </c>
       <c r="B27" t="n">
-        <v>91500</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,34 +3234,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490409</v>
+        <v>490313</v>
       </c>
       <c r="R27" t="n">
-        <v>7048125</v>
+        <v>7048263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,32 +3433,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845765</v>
+        <v>128845753</v>
       </c>
       <c r="B29" t="n">
-        <v>91039</v>
+        <v>91500</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5747</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3460,10 +3468,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490278</v>
+        <v>490409</v>
       </c>
       <c r="R29" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3526,53 +3534,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845780</v>
+        <v>128845765</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>91039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490313</v>
+        <v>490278</v>
       </c>
       <c r="R30" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R2" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>91958</v>
+        <v>92439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R3" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,53 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845758</v>
+        <v>128845756</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>91958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490634</v>
+        <v>490682</v>
       </c>
       <c r="R4" t="n">
-        <v>7047978</v>
+        <v>7048040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B7" t="n">
-        <v>92828</v>
+        <v>91500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R7" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B8" t="n">
-        <v>91500</v>
+        <v>92828</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R8" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845781</v>
+        <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>92201</v>
+        <v>91500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490331</v>
+        <v>490385</v>
       </c>
       <c r="R9" t="n">
-        <v>7048266</v>
+        <v>7048282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845750</v>
+        <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>91500</v>
+        <v>92201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490385</v>
+        <v>490331</v>
       </c>
       <c r="R10" t="n">
-        <v>7048282</v>
+        <v>7048266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B24" t="n">
-        <v>91800</v>
+        <v>92830</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R24" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B25" t="n">
-        <v>92830</v>
+        <v>91800</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R25" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845780</v>
+        <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>92828</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,42 +3234,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490313</v>
+        <v>490317</v>
       </c>
       <c r="R27" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845770</v>
+        <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>92828</v>
+        <v>91500</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3343,21 +3335,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490317</v>
+        <v>490409</v>
       </c>
       <c r="R28" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,32 +3425,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845753</v>
+        <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>91500</v>
+        <v>91039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5747</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,10 +3460,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490409</v>
+        <v>490278</v>
       </c>
       <c r="R29" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3534,45 +3526,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845765</v>
+        <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>91039</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490278</v>
+        <v>490313</v>
       </c>
       <c r="R30" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128845756</v>
       </c>
       <c r="B4" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>91500</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R7" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>92828</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R8" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845750</v>
+        <v>128845781</v>
       </c>
       <c r="B9" t="n">
-        <v>91500</v>
+        <v>92205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490385</v>
+        <v>490331</v>
       </c>
       <c r="R9" t="n">
-        <v>7048282</v>
+        <v>7048266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845781</v>
+        <v>128845750</v>
       </c>
       <c r="B10" t="n">
-        <v>92201</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490331</v>
+        <v>490385</v>
       </c>
       <c r="R10" t="n">
-        <v>7048266</v>
+        <v>7048282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
         <v>128845792</v>
       </c>
       <c r="B11" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>128845791</v>
       </c>
       <c r="B12" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845762</v>
+        <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>92823</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1805,25 +1805,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490673</v>
+        <v>490666</v>
       </c>
       <c r="R13" t="n">
-        <v>7047987</v>
+        <v>7048312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845761</v>
+        <v>128845762</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>92827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1897,42 +1914,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490666</v>
+        <v>490673</v>
       </c>
       <c r="R14" t="n">
-        <v>7048312</v>
+        <v>7047987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128845775</v>
       </c>
       <c r="B16" t="n">
-        <v>92828</v>
+        <v>92832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>128845774</v>
       </c>
       <c r="B17" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128845747</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128845760</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>92830</v>
+        <v>91804</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R24" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>91800</v>
+        <v>92834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R25" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>92828</v>
+        <v>92832</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>91500</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92828</v>
+        <v>92832</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845758</v>
+        <v>128845756</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490634</v>
+        <v>490682</v>
       </c>
       <c r="R2" t="n">
-        <v>7047978</v>
+        <v>7048040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -885,45 +877,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845756</v>
+        <v>128845758</v>
       </c>
       <c r="B4" t="n">
-        <v>91962</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490682</v>
+        <v>490634</v>
       </c>
       <c r="R4" t="n">
-        <v>7048040</v>
+        <v>7047978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1592,34 +1592,25 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B11" t="n">
-        <v>92787</v>
+        <v>92827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>150</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Grangråticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1627,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R11" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,45 +1684,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845791</v>
+        <v>128845761</v>
       </c>
       <c r="B12" t="n">
-        <v>92205</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490641</v>
+        <v>490666</v>
       </c>
       <c r="R12" t="n">
-        <v>7047962</v>
+        <v>7048312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,53 +1793,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845761</v>
+        <v>128845792</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>92787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490666</v>
+        <v>490278</v>
       </c>
       <c r="R13" t="n">
-        <v>7048312</v>
+        <v>7048250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,25 +1894,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845762</v>
+        <v>128845791</v>
       </c>
       <c r="B14" t="n">
-        <v>92827</v>
+        <v>92205</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>3298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490673</v>
+        <v>490641</v>
       </c>
       <c r="R14" t="n">
-        <v>7047987</v>
+        <v>7047962</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845770</v>
+        <v>128845765</v>
       </c>
       <c r="B27" t="n">
-        <v>92832</v>
+        <v>91043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490317</v>
+        <v>490278</v>
       </c>
       <c r="R27" t="n">
         <v>7048250</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845753</v>
+        <v>128845780</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,34 +3335,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490409</v>
+        <v>490313</v>
       </c>
       <c r="R28" t="n">
-        <v>7048125</v>
+        <v>7048263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,32 +3433,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845765</v>
+        <v>128845770</v>
       </c>
       <c r="B29" t="n">
-        <v>91043</v>
+        <v>92832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3460,7 +3468,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490278</v>
+        <v>490317</v>
       </c>
       <c r="R29" t="n">
         <v>7048250</v>
@@ -3526,10 +3534,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845780</v>
+        <v>128845753</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>91504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3537,42 +3545,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490313</v>
+        <v>490409</v>
       </c>
       <c r="R30" t="n">
-        <v>7048263</v>
+        <v>7048125</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R7" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>92832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R8" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845781</v>
+        <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>92205</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490331</v>
+        <v>490385</v>
       </c>
       <c r="R9" t="n">
-        <v>7048266</v>
+        <v>7048282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845750</v>
+        <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>92205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490385</v>
+        <v>490331</v>
       </c>
       <c r="R10" t="n">
-        <v>7048282</v>
+        <v>7048266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845762</v>
+        <v>128845761</v>
       </c>
       <c r="B11" t="n">
-        <v>92827</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,25 +1603,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490673</v>
+        <v>490666</v>
       </c>
       <c r="R11" t="n">
-        <v>7047987</v>
+        <v>7048312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,53 +1701,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845761</v>
+        <v>128845792</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>92787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490666</v>
+        <v>490278</v>
       </c>
       <c r="R12" t="n">
-        <v>7048312</v>
+        <v>7048250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845792</v>
+        <v>128845791</v>
       </c>
       <c r="B13" t="n">
-        <v>92787</v>
+        <v>92205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1828,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490278</v>
+        <v>490641</v>
       </c>
       <c r="R13" t="n">
-        <v>7048250</v>
+        <v>7047962</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,34 +1903,25 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845791</v>
+        <v>128845762</v>
       </c>
       <c r="B14" t="n">
-        <v>92205</v>
+        <v>92827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490641</v>
+        <v>490673</v>
       </c>
       <c r="R14" t="n">
-        <v>7047962</v>
+        <v>7047987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B22" t="n">
-        <v>91804</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,34 +2721,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R22" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>91804</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,42 +2830,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R23" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845780</v>
+        <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,42 +3335,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490313</v>
+        <v>490409</v>
       </c>
       <c r="R28" t="n">
-        <v>7048263</v>
+        <v>7048125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,10 +3526,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845753</v>
+        <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>91504</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3545,34 +3537,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490409</v>
+        <v>490313</v>
       </c>
       <c r="R30" t="n">
-        <v>7048125</v>
+        <v>7048263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128845756</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,45 +776,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B3" t="n">
-        <v>92443</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R3" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,53 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845758</v>
+        <v>128845754</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>92448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490634</v>
+        <v>490396</v>
       </c>
       <c r="R4" t="n">
-        <v>7047978</v>
+        <v>7048167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R7" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>92832</v>
+        <v>91509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R8" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,53 +1592,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845761</v>
+        <v>128845791</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>92210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490666</v>
+        <v>490641</v>
       </c>
       <c r="R11" t="n">
-        <v>7048312</v>
+        <v>7047962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,34 +1693,25 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B12" t="n">
-        <v>92787</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Grangråticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1736,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R12" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,45 +1785,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845791</v>
+        <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>92205</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490641</v>
+        <v>490666</v>
       </c>
       <c r="R13" t="n">
-        <v>7047962</v>
+        <v>7048312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,25 +1894,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845762</v>
+        <v>128845792</v>
       </c>
       <c r="B14" t="n">
-        <v>92827</v>
+        <v>92792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490673</v>
+        <v>490278</v>
       </c>
       <c r="R14" t="n">
-        <v>7047987</v>
+        <v>7048250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128845775</v>
       </c>
       <c r="B16" t="n">
-        <v>92832</v>
+        <v>92837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>128845774</v>
       </c>
       <c r="B17" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128845747</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>128845760</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>128845777</v>
       </c>
       <c r="B23" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845765</v>
+        <v>128845753</v>
       </c>
       <c r="B27" t="n">
-        <v>91043</v>
+        <v>91509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5747</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490278</v>
+        <v>490409</v>
       </c>
       <c r="R27" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845753</v>
+        <v>128845770</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>92837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490409</v>
+        <v>490317</v>
       </c>
       <c r="R28" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,32 +3425,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845770</v>
+        <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>92832</v>
+        <v>91048</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490317</v>
+        <v>490278</v>
       </c>
       <c r="R29" t="n">
         <v>7048250</v>
@@ -3529,7 +3529,7 @@
         <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92832</v>
+        <v>92837</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>91805</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,42 +2721,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R22" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B23" t="n">
-        <v>91805</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,34 +2822,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R23" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845765</v>
+        <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>91055</v>
+        <v>92845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490278</v>
+        <v>490317</v>
       </c>
       <c r="R27" t="n">
         <v>7048250</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845780</v>
+        <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>91516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,42 +3335,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490313</v>
+        <v>490409</v>
       </c>
       <c r="R28" t="n">
-        <v>7048263</v>
+        <v>7048125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,32 +3425,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845770</v>
+        <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>92845</v>
+        <v>91055</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,7 +3460,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490317</v>
+        <v>490278</v>
       </c>
       <c r="R29" t="n">
         <v>7048250</v>
@@ -3534,10 +3526,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845753</v>
+        <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>91516</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3545,34 +3537,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490409</v>
+        <v>490313</v>
       </c>
       <c r="R30" t="n">
-        <v>7048125</v>
+        <v>7048263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B2" t="n">
-        <v>91975</v>
+        <v>92461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R2" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845754</v>
+        <v>128845756</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>91978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490396</v>
+        <v>490682</v>
       </c>
       <c r="R3" t="n">
-        <v>7048167</v>
+        <v>7048040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B7" t="n">
-        <v>92845</v>
+        <v>91519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R7" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B8" t="n">
-        <v>91516</v>
+        <v>92850</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R8" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,32 +1592,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845791</v>
+        <v>128845792</v>
       </c>
       <c r="B11" t="n">
-        <v>92218</v>
+        <v>92805</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>150</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490641</v>
+        <v>490278</v>
       </c>
       <c r="R11" t="n">
-        <v>7047962</v>
+        <v>7048250</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,7 +1696,7 @@
         <v>128845762</v>
       </c>
       <c r="B12" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,32 +1785,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845792</v>
+        <v>128845791</v>
       </c>
       <c r="B13" t="n">
-        <v>92800</v>
+        <v>92223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490278</v>
+        <v>490641</v>
       </c>
       <c r="R13" t="n">
-        <v>7048250</v>
+        <v>7047962</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845775</v>
+        <v>128845774</v>
       </c>
       <c r="B16" t="n">
-        <v>92845</v>
+        <v>92223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490496</v>
+        <v>490453</v>
       </c>
       <c r="R16" t="n">
-        <v>7048026</v>
+        <v>7048050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,32 +2197,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845774</v>
+        <v>128845775</v>
       </c>
       <c r="B17" t="n">
-        <v>92218</v>
+        <v>92850</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490453</v>
+        <v>490496</v>
       </c>
       <c r="R17" t="n">
-        <v>7048050</v>
+        <v>7048026</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,45 +2500,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845790</v>
+        <v>128845747</v>
       </c>
       <c r="B20" t="n">
-        <v>92800</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>150</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490558</v>
+        <v>490412</v>
       </c>
       <c r="R20" t="n">
-        <v>7047986</v>
+        <v>7048136</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2601,53 +2609,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845747</v>
+        <v>128845790</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>92805</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490412</v>
+        <v>490558</v>
       </c>
       <c r="R21" t="n">
-        <v>7048136</v>
+        <v>7047986</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
         <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845770</v>
+        <v>128845753</v>
       </c>
       <c r="B27" t="n">
-        <v>92845</v>
+        <v>91519</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,21 +3234,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490317</v>
+        <v>490409</v>
       </c>
       <c r="R27" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845753</v>
+        <v>128845770</v>
       </c>
       <c r="B28" t="n">
-        <v>91516</v>
+        <v>92850</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490409</v>
+        <v>490317</v>
       </c>
       <c r="R28" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,45 +3425,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845765</v>
+        <v>128845780</v>
       </c>
       <c r="B29" t="n">
-        <v>91055</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490278</v>
+        <v>490313</v>
       </c>
       <c r="R29" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3526,53 +3534,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845780</v>
+        <v>128845765</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>91058</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490313</v>
+        <v>490278</v>
       </c>
       <c r="R30" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92845</v>
+        <v>92850</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845754</v>
+        <v>128845756</v>
       </c>
       <c r="B2" t="n">
-        <v>92461</v>
+        <v>91981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490396</v>
+        <v>490682</v>
       </c>
       <c r="R2" t="n">
-        <v>7048167</v>
+        <v>7048040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>91978</v>
+        <v>92464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R3" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>91519</v>
+        <v>92853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R7" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>92850</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R8" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845750</v>
+        <v>128845781</v>
       </c>
       <c r="B9" t="n">
-        <v>91519</v>
+        <v>92226</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490385</v>
+        <v>490331</v>
       </c>
       <c r="R9" t="n">
-        <v>7048282</v>
+        <v>7048266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845781</v>
+        <v>128845750</v>
       </c>
       <c r="B10" t="n">
-        <v>92223</v>
+        <v>91522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490331</v>
+        <v>490385</v>
       </c>
       <c r="R10" t="n">
-        <v>7048266</v>
+        <v>7048282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
         <v>128845792</v>
       </c>
       <c r="B11" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,25 +1693,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845762</v>
+        <v>128845791</v>
       </c>
       <c r="B12" t="n">
-        <v>92845</v>
+        <v>92226</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1719,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490673</v>
+        <v>490641</v>
       </c>
       <c r="R12" t="n">
-        <v>7047987</v>
+        <v>7047962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,34 +1794,25 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845791</v>
+        <v>128845762</v>
       </c>
       <c r="B13" t="n">
-        <v>92223</v>
+        <v>92848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490641</v>
+        <v>490673</v>
       </c>
       <c r="R13" t="n">
-        <v>7047962</v>
+        <v>7047987</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128845774</v>
       </c>
       <c r="B16" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>128845775</v>
       </c>
       <c r="B17" t="n">
-        <v>92850</v>
+        <v>92853</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,53 +2500,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845747</v>
+        <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>92808</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490412</v>
+        <v>490558</v>
       </c>
       <c r="R20" t="n">
-        <v>7048136</v>
+        <v>7047986</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,45 +2601,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845790</v>
+        <v>128845747</v>
       </c>
       <c r="B21" t="n">
-        <v>92805</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>150</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490558</v>
+        <v>490412</v>
       </c>
       <c r="R21" t="n">
-        <v>7047986</v>
+        <v>7048136</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
         <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B24" t="n">
-        <v>91808</v>
+        <v>92855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R24" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B25" t="n">
-        <v>92852</v>
+        <v>91811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R25" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845753</v>
+        <v>128845765</v>
       </c>
       <c r="B27" t="n">
-        <v>91519</v>
+        <v>91061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5747</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490409</v>
+        <v>490278</v>
       </c>
       <c r="R27" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845770</v>
+        <v>128845780</v>
       </c>
       <c r="B28" t="n">
-        <v>92850</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,34 +3335,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1968</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490317</v>
+        <v>490313</v>
       </c>
       <c r="R28" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,10 +3433,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845780</v>
+        <v>128845770</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>92853</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,42 +3444,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490313</v>
+        <v>490317</v>
       </c>
       <c r="R29" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845765</v>
+        <v>128845753</v>
       </c>
       <c r="B30" t="n">
-        <v>91058</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490278</v>
+        <v>490409</v>
       </c>
       <c r="R30" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92850</v>
+        <v>92853</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B2" t="n">
-        <v>91981</v>
+        <v>92464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R2" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845754</v>
+        <v>128845756</v>
       </c>
       <c r="B3" t="n">
-        <v>92464</v>
+        <v>91981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490396</v>
+        <v>490682</v>
       </c>
       <c r="R3" t="n">
-        <v>7048167</v>
+        <v>7048040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1592,32 +1592,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845792</v>
+        <v>128845791</v>
       </c>
       <c r="B11" t="n">
-        <v>92808</v>
+        <v>92226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>150</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490278</v>
+        <v>490641</v>
       </c>
       <c r="R11" t="n">
-        <v>7048250</v>
+        <v>7047962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,32 +1693,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845791</v>
+        <v>128845792</v>
       </c>
       <c r="B12" t="n">
-        <v>92226</v>
+        <v>92808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>150</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490641</v>
+        <v>490278</v>
       </c>
       <c r="R12" t="n">
-        <v>7047962</v>
+        <v>7048250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845762</v>
+        <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>92848</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1805,25 +1805,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490673</v>
+        <v>490666</v>
       </c>
       <c r="R13" t="n">
-        <v>7047987</v>
+        <v>7048312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845761</v>
+        <v>128845762</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>92848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1897,42 +1914,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490666</v>
+        <v>490673</v>
       </c>
       <c r="R14" t="n">
-        <v>7048312</v>
+        <v>7047987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B22" t="n">
-        <v>91811</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,34 +2721,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R22" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>91811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,42 +2830,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R23" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3223,32 +3223,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845765</v>
+        <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>91061</v>
+        <v>92853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490278</v>
+        <v>490317</v>
       </c>
       <c r="R27" t="n">
         <v>7048250</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845780</v>
+        <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,42 +3335,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490313</v>
+        <v>490409</v>
       </c>
       <c r="R28" t="n">
-        <v>7048263</v>
+        <v>7048125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,10 +3425,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845770</v>
+        <v>128845780</v>
       </c>
       <c r="B29" t="n">
-        <v>92853</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3444,34 +3436,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490317</v>
+        <v>490313</v>
       </c>
       <c r="R29" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845753</v>
+        <v>128845765</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>91061</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490409</v>
+        <v>490278</v>
       </c>
       <c r="R30" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -2920,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>92855</v>
+        <v>91811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R24" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>91811</v>
+        <v>92855</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R25" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845770</v>
+        <v>128845753</v>
       </c>
       <c r="B27" t="n">
-        <v>92853</v>
+        <v>91522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,21 +3234,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490317</v>
+        <v>490409</v>
       </c>
       <c r="R27" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845753</v>
+        <v>128845780</v>
       </c>
       <c r="B28" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,34 +3335,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490409</v>
+        <v>490313</v>
       </c>
       <c r="R28" t="n">
-        <v>7048125</v>
+        <v>7048263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,10 +3433,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845780</v>
+        <v>128845770</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>92853</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,42 +3444,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490313</v>
+        <v>490317</v>
       </c>
       <c r="R29" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>92464</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R2" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>92464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R3" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,53 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845758</v>
+        <v>128845756</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>91981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490634</v>
+        <v>490682</v>
       </c>
       <c r="R4" t="n">
-        <v>7047978</v>
+        <v>7048040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B7" t="n">
-        <v>92853</v>
+        <v>91522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R7" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>92853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R8" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1592,32 +1592,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845791</v>
+        <v>128845792</v>
       </c>
       <c r="B11" t="n">
-        <v>92226</v>
+        <v>92808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>150</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490641</v>
+        <v>490278</v>
       </c>
       <c r="R11" t="n">
-        <v>7047962</v>
+        <v>7048250</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,34 +1693,25 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B12" t="n">
-        <v>92808</v>
+        <v>92848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Grangråticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1728,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R12" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,25 +1894,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845762</v>
+        <v>128845791</v>
       </c>
       <c r="B14" t="n">
-        <v>92848</v>
+        <v>92226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>3298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490673</v>
+        <v>490641</v>
       </c>
       <c r="R14" t="n">
-        <v>7047987</v>
+        <v>7047962</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>91811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,42 +2721,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R22" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B23" t="n">
-        <v>91811</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,34 +2822,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R23" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845780</v>
+        <v>128845770</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>92853</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,42 +3335,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490313</v>
+        <v>490317</v>
       </c>
       <c r="R28" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,32 +3425,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845770</v>
+        <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>92853</v>
+        <v>91061</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,7 +3460,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490317</v>
+        <v>490278</v>
       </c>
       <c r="R29" t="n">
         <v>7048250</v>
@@ -3534,45 +3526,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845765</v>
+        <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>91061</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490278</v>
+        <v>490313</v>
       </c>
       <c r="R30" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845758</v>
+        <v>128845754</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>92471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490634</v>
+        <v>490396</v>
       </c>
       <c r="R2" t="n">
-        <v>7047978</v>
+        <v>7048167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,45 +776,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B3" t="n">
-        <v>92464</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R3" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
         <v>128845756</v>
       </c>
       <c r="B4" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>91522</v>
+        <v>92860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R7" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>92853</v>
+        <v>91529</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R8" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>128845781</v>
       </c>
       <c r="B9" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128845750</v>
       </c>
       <c r="B10" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128845792</v>
       </c>
       <c r="B11" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>128845762</v>
       </c>
       <c r="B12" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>128845791</v>
       </c>
       <c r="B14" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128845774</v>
       </c>
       <c r="B16" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>128845775</v>
       </c>
       <c r="B17" t="n">
-        <v>92853</v>
+        <v>92860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128845747</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B22" t="n">
-        <v>91811</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,34 +2721,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R22" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>91818</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,42 +2830,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R23" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B24" t="n">
-        <v>91811</v>
+        <v>92862</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R24" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B25" t="n">
-        <v>92855</v>
+        <v>91818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R25" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845753</v>
+        <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>91522</v>
+        <v>92860</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,21 +3234,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490409</v>
+        <v>490317</v>
       </c>
       <c r="R27" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845770</v>
+        <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>92853</v>
+        <v>91529</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490317</v>
+        <v>490409</v>
       </c>
       <c r="R28" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3428,7 +3428,7 @@
         <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92853</v>
+        <v>92860</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -1592,32 +1592,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845792</v>
+        <v>128845791</v>
       </c>
       <c r="B11" t="n">
-        <v>92815</v>
+        <v>92233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>150</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490278</v>
+        <v>490641</v>
       </c>
       <c r="R11" t="n">
-        <v>7048250</v>
+        <v>7047962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,25 +1693,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845762</v>
+        <v>128845792</v>
       </c>
       <c r="B12" t="n">
-        <v>92855</v>
+        <v>92815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>150</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1719,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490673</v>
+        <v>490278</v>
       </c>
       <c r="R12" t="n">
-        <v>7047987</v>
+        <v>7048250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,10 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845761</v>
+        <v>128845762</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>92855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,42 +1805,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490666</v>
+        <v>490673</v>
       </c>
       <c r="R13" t="n">
-        <v>7048312</v>
+        <v>7047987</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,45 +1886,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845791</v>
+        <v>128845761</v>
       </c>
       <c r="B14" t="n">
-        <v>92233</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490641</v>
+        <v>490666</v>
       </c>
       <c r="R14" t="n">
-        <v>7047962</v>
+        <v>7048312</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>91818</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,42 +2721,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R22" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B23" t="n">
-        <v>91818</v>
+        <v>57722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,34 +2822,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R23" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>92862</v>
+        <v>91818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R24" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>91818</v>
+        <v>92862</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R25" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>92471</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R2" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,53 +784,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845758</v>
+        <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>92478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490634</v>
+        <v>490396</v>
       </c>
       <c r="R3" t="n">
-        <v>7047978</v>
+        <v>7048167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
         <v>128845756</v>
       </c>
       <c r="B4" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>92860</v>
+        <v>92867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845781</v>
+        <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>92233</v>
+        <v>91536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490331</v>
+        <v>490385</v>
       </c>
       <c r="R9" t="n">
-        <v>7048266</v>
+        <v>7048282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845750</v>
+        <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>91529</v>
+        <v>92240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490385</v>
+        <v>490331</v>
       </c>
       <c r="R10" t="n">
-        <v>7048282</v>
+        <v>7048266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
         <v>128845791</v>
       </c>
       <c r="B11" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,34 +1693,25 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B12" t="n">
-        <v>92815</v>
+        <v>92862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Grangråticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1728,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R12" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,10 +1785,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845762</v>
+        <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>92855</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1805,25 +1796,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490673</v>
+        <v>490666</v>
       </c>
       <c r="R13" t="n">
-        <v>7047987</v>
+        <v>7048312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,53 +1894,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845761</v>
+        <v>128845792</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>92822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490666</v>
+        <v>490278</v>
       </c>
       <c r="R14" t="n">
-        <v>7048312</v>
+        <v>7048250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845774</v>
+        <v>128845775</v>
       </c>
       <c r="B16" t="n">
-        <v>92233</v>
+        <v>92867</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490453</v>
+        <v>490496</v>
       </c>
       <c r="R16" t="n">
-        <v>7048050</v>
+        <v>7048026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,32 +2197,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845775</v>
+        <v>128845774</v>
       </c>
       <c r="B17" t="n">
-        <v>92860</v>
+        <v>92240</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490496</v>
+        <v>490453</v>
       </c>
       <c r="R17" t="n">
-        <v>7048026</v>
+        <v>7048050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845770</v>
+        <v>128845753</v>
       </c>
       <c r="B27" t="n">
-        <v>92860</v>
+        <v>91536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,21 +3234,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490317</v>
+        <v>490409</v>
       </c>
       <c r="R27" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845753</v>
+        <v>128845780</v>
       </c>
       <c r="B28" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,34 +3335,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490409</v>
+        <v>490313</v>
       </c>
       <c r="R28" t="n">
-        <v>7048125</v>
+        <v>7048263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,32 +3433,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845765</v>
+        <v>128845770</v>
       </c>
       <c r="B29" t="n">
-        <v>91065</v>
+        <v>92867</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3460,7 +3468,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490278</v>
+        <v>490317</v>
       </c>
       <c r="R29" t="n">
         <v>7048250</v>
@@ -3526,53 +3534,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845780</v>
+        <v>128845765</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>91072</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490313</v>
+        <v>490278</v>
       </c>
       <c r="R30" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92860</v>
+        <v>92867</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845758</v>
+        <v>128845756</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>91997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490634</v>
+        <v>490682</v>
       </c>
       <c r="R2" t="n">
-        <v>7047978</v>
+        <v>7048040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,45 +776,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B3" t="n">
-        <v>92478</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R3" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,32 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>92480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R4" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B7" t="n">
-        <v>92867</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R7" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B8" t="n">
-        <v>91536</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R8" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128845791</v>
       </c>
       <c r="B11" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845762</v>
+        <v>128845761</v>
       </c>
       <c r="B12" t="n">
-        <v>92862</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1704,25 +1704,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490673</v>
+        <v>490666</v>
       </c>
       <c r="R12" t="n">
-        <v>7047987</v>
+        <v>7048312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,53 +1802,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845761</v>
+        <v>128845792</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>92824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490666</v>
+        <v>490278</v>
       </c>
       <c r="R13" t="n">
-        <v>7048312</v>
+        <v>7048250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,34 +1903,25 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B14" t="n">
-        <v>92822</v>
+        <v>92864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Grangråticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R14" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845775</v>
+        <v>128845774</v>
       </c>
       <c r="B16" t="n">
-        <v>92867</v>
+        <v>92242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490496</v>
+        <v>490453</v>
       </c>
       <c r="R16" t="n">
-        <v>7048026</v>
+        <v>7048050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,32 +2197,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845774</v>
+        <v>128845775</v>
       </c>
       <c r="B17" t="n">
-        <v>92240</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490453</v>
+        <v>490496</v>
       </c>
       <c r="R17" t="n">
-        <v>7048050</v>
+        <v>7048026</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,45 +2500,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845790</v>
+        <v>128845747</v>
       </c>
       <c r="B20" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>150</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490558</v>
+        <v>490412</v>
       </c>
       <c r="R20" t="n">
-        <v>7047986</v>
+        <v>7048136</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2601,53 +2609,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845747</v>
+        <v>128845790</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>92824</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490412</v>
+        <v>490558</v>
       </c>
       <c r="R21" t="n">
-        <v>7048136</v>
+        <v>7047986</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
         <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>128845760</v>
       </c>
       <c r="B23" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>128845753</v>
       </c>
       <c r="B27" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845780</v>
+        <v>128845770</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>92869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,42 +3335,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490313</v>
+        <v>490317</v>
       </c>
       <c r="R28" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,32 +3425,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845770</v>
+        <v>128845765</v>
       </c>
       <c r="B29" t="n">
-        <v>92867</v>
+        <v>91074</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3468,7 +3460,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490317</v>
+        <v>490278</v>
       </c>
       <c r="R29" t="n">
         <v>7048250</v>
@@ -3534,45 +3526,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845765</v>
+        <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>91072</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490278</v>
+        <v>490313</v>
       </c>
       <c r="R30" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92867</v>
+        <v>92869</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845756</v>
+        <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490682</v>
+        <v>490634</v>
       </c>
       <c r="R2" t="n">
-        <v>7048040</v>
+        <v>7047978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,53 +784,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845758</v>
+        <v>128845756</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>91997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490634</v>
+        <v>490682</v>
       </c>
       <c r="R3" t="n">
-        <v>7047978</v>
+        <v>7048040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R7" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R8" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1592,34 +1592,25 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845791</v>
+        <v>128845762</v>
       </c>
       <c r="B11" t="n">
-        <v>92242</v>
+        <v>92864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1627,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490641</v>
+        <v>490673</v>
       </c>
       <c r="R11" t="n">
-        <v>7047962</v>
+        <v>7047987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,53 +1684,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845761</v>
+        <v>128845791</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490666</v>
+        <v>490641</v>
       </c>
       <c r="R12" t="n">
-        <v>7048312</v>
+        <v>7047962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,45 +1785,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845792</v>
+        <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>92824</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490278</v>
+        <v>490666</v>
       </c>
       <c r="R13" t="n">
-        <v>7048250</v>
+        <v>7048312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,25 +1894,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845762</v>
+        <v>128845792</v>
       </c>
       <c r="B14" t="n">
-        <v>92864</v>
+        <v>92824</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490673</v>
+        <v>490278</v>
       </c>
       <c r="R14" t="n">
-        <v>7047987</v>
+        <v>7048250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,32 +2096,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845774</v>
+        <v>128845775</v>
       </c>
       <c r="B16" t="n">
-        <v>92242</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490453</v>
+        <v>490496</v>
       </c>
       <c r="R16" t="n">
-        <v>7048050</v>
+        <v>7048026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,32 +2197,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845775</v>
+        <v>128845774</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490496</v>
+        <v>490453</v>
       </c>
       <c r="R17" t="n">
-        <v>7048026</v>
+        <v>7048050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B22" t="n">
-        <v>91827</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,34 +2721,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R22" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>91827</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,42 +2830,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R23" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,32 +2920,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B24" t="n">
-        <v>91827</v>
+        <v>92871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R24" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B25" t="n">
-        <v>92871</v>
+        <v>91827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R25" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845753</v>
+        <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>91538</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,21 +3234,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490409</v>
+        <v>490317</v>
       </c>
       <c r="R27" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845770</v>
+        <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>92869</v>
+        <v>91538</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490317</v>
+        <v>490409</v>
       </c>
       <c r="R28" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845758</v>
+        <v>128845756</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>91997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490634</v>
+        <v>490682</v>
       </c>
       <c r="R2" t="n">
-        <v>7047978</v>
+        <v>7048040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>91997</v>
+        <v>92480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R3" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,45 +877,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B4" t="n">
-        <v>92480</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R4" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R7" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R8" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>91827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,42 +2721,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R22" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,10 +2811,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B23" t="n">
-        <v>91827</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,34 +2822,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R23" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128845756</v>
       </c>
       <c r="B2" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -779,7 +779,7 @@
         <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845746</v>
+        <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>92855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490472</v>
+        <v>490560</v>
       </c>
       <c r="R7" t="n">
-        <v>7048031</v>
+        <v>7047985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845748</v>
+        <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>91536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,21 +1300,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490560</v>
+        <v>490472</v>
       </c>
       <c r="R8" t="n">
-        <v>7047985</v>
+        <v>7048031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,25 +1592,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845762</v>
+        <v>128845791</v>
       </c>
       <c r="B11" t="n">
-        <v>92864</v>
+        <v>92257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>3298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1618,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490673</v>
+        <v>490641</v>
       </c>
       <c r="R11" t="n">
-        <v>7047987</v>
+        <v>7047962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,45 +1693,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845791</v>
+        <v>128845761</v>
       </c>
       <c r="B12" t="n">
-        <v>92242</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490641</v>
+        <v>490666</v>
       </c>
       <c r="R12" t="n">
-        <v>7047962</v>
+        <v>7048312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,53 +1802,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845761</v>
+        <v>128845792</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>92810</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490666</v>
+        <v>490278</v>
       </c>
       <c r="R13" t="n">
-        <v>7048312</v>
+        <v>7048250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,34 +1903,25 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B14" t="n">
-        <v>92824</v>
+        <v>92850</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Grangråticka</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R14" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>128845775</v>
       </c>
       <c r="B16" t="n">
-        <v>92869</v>
+        <v>92855</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>128845774</v>
       </c>
       <c r="B17" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,53 +2500,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845747</v>
+        <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>92810</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490412</v>
+        <v>490558</v>
       </c>
       <c r="R20" t="n">
-        <v>7048136</v>
+        <v>7047986</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,45 +2601,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845790</v>
+        <v>128845747</v>
       </c>
       <c r="B21" t="n">
-        <v>92824</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>150</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490558</v>
+        <v>490412</v>
       </c>
       <c r="R21" t="n">
-        <v>7047986</v>
+        <v>7048136</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
         <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>128845752</v>
       </c>
       <c r="B24" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128845772</v>
       </c>
       <c r="B25" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>92869</v>
+        <v>92855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3425,45 +3425,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845765</v>
+        <v>128845780</v>
       </c>
       <c r="B29" t="n">
-        <v>91074</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490278</v>
+        <v>490313</v>
       </c>
       <c r="R29" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3526,53 +3534,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845780</v>
+        <v>128845765</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490313</v>
+        <v>490278</v>
       </c>
       <c r="R30" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92869</v>
+        <v>92855</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845756</v>
+        <v>128845754</v>
       </c>
       <c r="B2" t="n">
-        <v>91992</v>
+        <v>92495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490682</v>
+        <v>490396</v>
       </c>
       <c r="R2" t="n">
-        <v>7048040</v>
+        <v>7048167</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845754</v>
+        <v>128845758</v>
       </c>
       <c r="B3" t="n">
-        <v>92494</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490396</v>
+        <v>490634</v>
       </c>
       <c r="R3" t="n">
-        <v>7048167</v>
+        <v>7047978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,53 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845758</v>
+        <v>128845756</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490634</v>
+        <v>490682</v>
       </c>
       <c r="R4" t="n">
-        <v>7047978</v>
+        <v>7048040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845750</v>
+        <v>128845781</v>
       </c>
       <c r="B9" t="n">
-        <v>91536</v>
+        <v>92258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490385</v>
+        <v>490331</v>
       </c>
       <c r="R9" t="n">
-        <v>7048282</v>
+        <v>7048266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845781</v>
+        <v>128845750</v>
       </c>
       <c r="B10" t="n">
-        <v>92257</v>
+        <v>91536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490331</v>
+        <v>490385</v>
       </c>
       <c r="R10" t="n">
-        <v>7048266</v>
+        <v>7048282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,34 +1592,30 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845791</v>
+        <v>128845762</v>
       </c>
       <c r="B11" t="n">
-        <v>92257</v>
+        <v>92851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1627,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490641</v>
+        <v>490673</v>
       </c>
       <c r="R11" t="n">
-        <v>7047962</v>
+        <v>7047987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,53 +1689,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845761</v>
+        <v>128845791</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490666</v>
+        <v>490641</v>
       </c>
       <c r="R12" t="n">
-        <v>7048312</v>
+        <v>7047962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,45 +1790,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845792</v>
+        <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>92810</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490278</v>
+        <v>490666</v>
       </c>
       <c r="R13" t="n">
-        <v>7048250</v>
+        <v>7048312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,25 +1899,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845762</v>
+        <v>128845792</v>
       </c>
       <c r="B14" t="n">
-        <v>92850</v>
+        <v>92811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1929,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490673</v>
+        <v>490278</v>
       </c>
       <c r="R14" t="n">
-        <v>7047987</v>
+        <v>7048250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +2003,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,32 +2101,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128845775</v>
+        <v>128845774</v>
       </c>
       <c r="B16" t="n">
-        <v>92855</v>
+        <v>92258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2136,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490496</v>
+        <v>490453</v>
       </c>
       <c r="R16" t="n">
-        <v>7048026</v>
+        <v>7048050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,32 +2202,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845774</v>
+        <v>128845775</v>
       </c>
       <c r="B17" t="n">
-        <v>92257</v>
+        <v>92856</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2232,10 +2237,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490453</v>
+        <v>490496</v>
       </c>
       <c r="R17" t="n">
-        <v>7048050</v>
+        <v>7048026</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,7 +2306,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2407,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,14 +2424,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2503,7 +2504,7 @@
         <v>128845790</v>
       </c>
       <c r="B20" t="n">
-        <v>92810</v>
+        <v>92811</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,7 +2714,7 @@
         <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,32 +2921,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845752</v>
+        <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>92857</v>
+        <v>91838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2955,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490304</v>
+        <v>490686</v>
       </c>
       <c r="R24" t="n">
-        <v>7048251</v>
+        <v>7048041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,32 +3022,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>91837</v>
+        <v>92858</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R25" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3126,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,10 +3224,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845770</v>
+        <v>128845753</v>
       </c>
       <c r="B27" t="n">
-        <v>92855</v>
+        <v>91536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,21 +3235,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3258,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490317</v>
+        <v>490409</v>
       </c>
       <c r="R27" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,32 +3325,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845753</v>
+        <v>128845765</v>
       </c>
       <c r="B28" t="n">
-        <v>91536</v>
+        <v>91075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5747</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3359,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490409</v>
+        <v>490278</v>
       </c>
       <c r="R28" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3425,10 +3426,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845780</v>
+        <v>128845770</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>92856</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,42 +3437,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490313</v>
+        <v>490317</v>
       </c>
       <c r="R29" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3534,45 +3527,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845765</v>
+        <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>91075</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490278</v>
+        <v>490313</v>
       </c>
       <c r="R30" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,7 +3639,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845754</v>
+        <v>128845756</v>
       </c>
       <c r="B2" t="n">
-        <v>92495</v>
+        <v>91993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490396</v>
+        <v>490682</v>
       </c>
       <c r="R2" t="n">
-        <v>7048167</v>
+        <v>7048040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,53 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845758</v>
+        <v>128845754</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>92495</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490634</v>
+        <v>490396</v>
       </c>
       <c r="R3" t="n">
-        <v>7047978</v>
+        <v>7048167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,45 +877,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845756</v>
+        <v>128845758</v>
       </c>
       <c r="B4" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490682</v>
+        <v>490634</v>
       </c>
       <c r="R4" t="n">
-        <v>7048040</v>
+        <v>7047978</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845781</v>
+        <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>92258</v>
+        <v>91536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490331</v>
+        <v>490385</v>
       </c>
       <c r="R9" t="n">
-        <v>7048266</v>
+        <v>7048282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845750</v>
+        <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>91536</v>
+        <v>92258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490385</v>
+        <v>490331</v>
       </c>
       <c r="R10" t="n">
-        <v>7048282</v>
+        <v>7048266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845762</v>
+        <v>128845761</v>
       </c>
       <c r="B11" t="n">
-        <v>92851</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,30 +1603,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490673</v>
+        <v>490666</v>
       </c>
       <c r="R11" t="n">
-        <v>7047987</v>
+        <v>7048312</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,32 +1701,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845791</v>
+        <v>128845792</v>
       </c>
       <c r="B12" t="n">
-        <v>92258</v>
+        <v>92811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>150</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1724,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490641</v>
+        <v>490278</v>
       </c>
       <c r="R12" t="n">
-        <v>7047962</v>
+        <v>7048250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,53 +1802,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845761</v>
+        <v>128845791</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>92258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490666</v>
+        <v>490641</v>
       </c>
       <c r="R13" t="n">
-        <v>7048312</v>
+        <v>7047962</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,34 +1903,30 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B14" t="n">
-        <v>92811</v>
+        <v>92851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R14" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,34 +2722,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R22" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>91838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,42 +2831,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R23" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3426,10 +3426,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845770</v>
+        <v>128845780</v>
       </c>
       <c r="B29" t="n">
-        <v>92856</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3437,34 +3437,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490317</v>
+        <v>490313</v>
       </c>
       <c r="R29" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3527,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845780</v>
+        <v>128845770</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>92856</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3538,42 +3546,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490313</v>
+        <v>490317</v>
       </c>
       <c r="R30" t="n">
-        <v>7048263</v>
+        <v>7048250</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845756</v>
+        <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490682</v>
+        <v>490634</v>
       </c>
       <c r="R2" t="n">
-        <v>7048040</v>
+        <v>7047978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845754</v>
+        <v>128845756</v>
       </c>
       <c r="B3" t="n">
-        <v>92495</v>
+        <v>91996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490396</v>
+        <v>490682</v>
       </c>
       <c r="R3" t="n">
-        <v>7048167</v>
+        <v>7048040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,53 +885,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845758</v>
+        <v>128845754</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>92498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490634</v>
+        <v>490396</v>
       </c>
       <c r="R4" t="n">
-        <v>7047978</v>
+        <v>7048167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>128845766</v>
       </c>
       <c r="B5" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>128845773</v>
       </c>
       <c r="B6" t="n">
-        <v>91075</v>
+        <v>91078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128845748</v>
       </c>
       <c r="B7" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128845746</v>
       </c>
       <c r="B8" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128845750</v>
       </c>
       <c r="B9" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128845781</v>
       </c>
       <c r="B10" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,53 +1592,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845761</v>
+        <v>128845791</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490666</v>
+        <v>490641</v>
       </c>
       <c r="R11" t="n">
-        <v>7048312</v>
+        <v>7047962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,34 +1693,30 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845792</v>
+        <v>128845762</v>
       </c>
       <c r="B12" t="n">
-        <v>92811</v>
+        <v>92854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1736,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490278</v>
+        <v>490673</v>
       </c>
       <c r="R12" t="n">
-        <v>7048250</v>
+        <v>7047987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,45 +1790,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845791</v>
+        <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>92258</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490641</v>
+        <v>490666</v>
       </c>
       <c r="R13" t="n">
-        <v>7047962</v>
+        <v>7048312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,30 +1899,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845762</v>
+        <v>128845792</v>
       </c>
       <c r="B14" t="n">
-        <v>92851</v>
+        <v>92814</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>150</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490673</v>
+        <v>490278</v>
       </c>
       <c r="R14" t="n">
-        <v>7047987</v>
+        <v>7048250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,7 +2003,7 @@
         <v>128845782</v>
       </c>
       <c r="B15" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>128845774</v>
       </c>
       <c r="B16" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>128845775</v>
       </c>
       <c r="B17" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128845769</v>
       </c>
       <c r="B18" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>128845786</v>
       </c>
       <c r="B19" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,45 +2501,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845790</v>
+        <v>128845747</v>
       </c>
       <c r="B20" t="n">
-        <v>92811</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>150</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490558</v>
+        <v>490412</v>
       </c>
       <c r="R20" t="n">
-        <v>7047986</v>
+        <v>7048136</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,53 +2610,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845747</v>
+        <v>128845790</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>92814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490412</v>
+        <v>490558</v>
       </c>
       <c r="R21" t="n">
-        <v>7048136</v>
+        <v>7047986</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845760</v>
+        <v>128845777</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>91841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,42 +2722,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490651</v>
+        <v>490614</v>
       </c>
       <c r="R22" t="n">
-        <v>7048287</v>
+        <v>7048276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845777</v>
+        <v>128845760</v>
       </c>
       <c r="B23" t="n">
-        <v>91838</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2831,34 +2823,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490614</v>
+        <v>490651</v>
       </c>
       <c r="R23" t="n">
-        <v>7048276</v>
+        <v>7048287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,7 +2924,7 @@
         <v>128845772</v>
       </c>
       <c r="B24" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128845752</v>
       </c>
       <c r="B25" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>128845757</v>
       </c>
       <c r="B26" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845753</v>
+        <v>128845770</v>
       </c>
       <c r="B27" t="n">
-        <v>91536</v>
+        <v>92859</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3235,21 +3235,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>1968</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490409</v>
+        <v>490317</v>
       </c>
       <c r="R27" t="n">
-        <v>7048125</v>
+        <v>7048250</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3325,32 +3325,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845765</v>
+        <v>128845753</v>
       </c>
       <c r="B28" t="n">
-        <v>91075</v>
+        <v>91539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5747</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490278</v>
+        <v>490409</v>
       </c>
       <c r="R28" t="n">
-        <v>7048250</v>
+        <v>7048125</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3535,32 +3535,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845770</v>
+        <v>128845765</v>
       </c>
       <c r="B30" t="n">
-        <v>92856</v>
+        <v>91078</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490317</v>
+        <v>490278</v>
       </c>
       <c r="R30" t="n">
         <v>7048250</v>
@@ -3639,7 +3639,7 @@
         <v>128845789</v>
       </c>
       <c r="B31" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>128845747</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>128845780</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>128845747</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>128845780</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128845758</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>128845761</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>128845747</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>128845780</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128845758</v>
+        <v>128845790</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490634</v>
+        <v>490558</v>
       </c>
       <c r="R2" t="n">
-        <v>7047978</v>
+        <v>7047986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128845756</v>
+        <v>128845792</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490682</v>
+        <v>490278</v>
       </c>
       <c r="R3" t="n">
-        <v>7048040</v>
+        <v>7048250</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128845754</v>
+        <v>128845772</v>
       </c>
       <c r="B4" t="n">
-        <v>92498</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490396</v>
+        <v>490686</v>
       </c>
       <c r="R4" t="n">
-        <v>7048167</v>
+        <v>7048041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128845766</v>
+        <v>128845777</v>
       </c>
       <c r="B5" t="n">
-        <v>91539</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490629</v>
+        <v>490614</v>
       </c>
       <c r="R5" t="n">
-        <v>7048267</v>
+        <v>7048276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128845773</v>
+        <v>128845746</v>
       </c>
       <c r="B6" t="n">
-        <v>91078</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5747</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490311</v>
+        <v>490472</v>
       </c>
       <c r="R6" t="n">
-        <v>7048265</v>
+        <v>7048031</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128845748</v>
+        <v>128845750</v>
       </c>
       <c r="B7" t="n">
-        <v>92859</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1968</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490560</v>
+        <v>490385</v>
       </c>
       <c r="R7" t="n">
-        <v>7047985</v>
+        <v>7048282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128845746</v>
+        <v>128845753</v>
       </c>
       <c r="B8" t="n">
-        <v>91539</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490472</v>
+        <v>490409</v>
       </c>
       <c r="R8" t="n">
-        <v>7048031</v>
+        <v>7048125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128845750</v>
+        <v>128845766</v>
       </c>
       <c r="B9" t="n">
-        <v>91539</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490385</v>
+        <v>490629</v>
       </c>
       <c r="R9" t="n">
-        <v>7048282</v>
+        <v>7048267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128845781</v>
+        <v>128845756</v>
       </c>
       <c r="B10" t="n">
-        <v>92261</v>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490331</v>
+        <v>490682</v>
       </c>
       <c r="R10" t="n">
-        <v>7048266</v>
+        <v>7048040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,45 +1584,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128845791</v>
+        <v>17133733</v>
       </c>
       <c r="B11" t="n">
-        <v>92261</v>
+        <v>110500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Jämtlandsmaskros</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Taraxacum crocodes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Dahlst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Töjsan, Jmt</t>
+          <t>Knutbränna /2 km SV/, Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490641</v>
+        <v>490581</v>
       </c>
       <c r="R11" t="n">
-        <v>7047962</v>
+        <v>7047937</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,12 +1649,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>1993-07-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>1993-07-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Trakt: 20F0a11, taxyta: S1430. 2x(5X10 m) Strand +grund lagun. Översvämmas vid högvatten. En bäver bor helt nära ytan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,30 +1670,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Älvstrand</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+          <t>Lars-Åke Bäckström, Nils Dahlberg, Lisbeth Berntsson, Eva Jonsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128845762</v>
+        <v>128845748</v>
       </c>
       <c r="B12" t="n">
-        <v>92854</v>
+        <v>93231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1704,19 +1702,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>1968</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1724,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490673</v>
+        <v>490560</v>
       </c>
       <c r="R12" t="n">
-        <v>7047987</v>
+        <v>7047985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128845761</v>
+        <v>128845770</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>93231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1801,42 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1968</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490666</v>
+        <v>490317</v>
       </c>
       <c r="R13" t="n">
-        <v>7048312</v>
+        <v>7048250</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,32 +1893,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128845792</v>
+        <v>128845775</v>
       </c>
       <c r="B14" t="n">
-        <v>92814</v>
+        <v>93231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
+        <v>1968</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1928,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490278</v>
+        <v>490496</v>
       </c>
       <c r="R14" t="n">
-        <v>7048250</v>
+        <v>7048026</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,32 +1994,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128845782</v>
+        <v>128845789</v>
       </c>
       <c r="B15" t="n">
-        <v>92861</v>
+        <v>93231</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>1968</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2035,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490634</v>
+        <v>490532</v>
       </c>
       <c r="R15" t="n">
-        <v>7047955</v>
+        <v>7048001</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,7 +2098,7 @@
         <v>128845774</v>
       </c>
       <c r="B16" t="n">
-        <v>92261</v>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,32 +2196,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128845775</v>
+        <v>128845781</v>
       </c>
       <c r="B17" t="n">
-        <v>92859</v>
+        <v>92632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2237,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490496</v>
+        <v>490331</v>
       </c>
       <c r="R17" t="n">
-        <v>7048026</v>
+        <v>7048266</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2303,10 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128845769</v>
+        <v>128845791</v>
       </c>
       <c r="B18" t="n">
-        <v>92498</v>
+        <v>92632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2314,21 +2308,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2338,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490305</v>
+        <v>490641</v>
       </c>
       <c r="R18" t="n">
-        <v>7048248</v>
+        <v>7047962</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2404,10 +2398,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128845786</v>
+        <v>128845757</v>
       </c>
       <c r="B19" t="n">
-        <v>91563</v>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,19 +2409,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2435,10 +2433,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490385</v>
+        <v>490551</v>
       </c>
       <c r="R19" t="n">
-        <v>7048283</v>
+        <v>7047983</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,53 +2499,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128845747</v>
+        <v>128845754</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490412</v>
+        <v>490396</v>
       </c>
       <c r="R20" t="n">
-        <v>7048136</v>
+        <v>7048167</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,32 +2600,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128845790</v>
+        <v>128845769</v>
       </c>
       <c r="B21" t="n">
-        <v>92814</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>150</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2635,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490558</v>
+        <v>490305</v>
       </c>
       <c r="R21" t="n">
-        <v>7047986</v>
+        <v>7048248</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2701,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128845777</v>
+        <v>128845765</v>
       </c>
       <c r="B22" t="n">
-        <v>91841</v>
+        <v>91435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2736,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490614</v>
+        <v>490278</v>
       </c>
       <c r="R22" t="n">
-        <v>7048276</v>
+        <v>7048250</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,53 +2802,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128845760</v>
+        <v>128845773</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>91435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5747</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490651</v>
+        <v>490311</v>
       </c>
       <c r="R23" t="n">
-        <v>7048287</v>
+        <v>7048265</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,10 +2903,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128845772</v>
+        <v>128845752</v>
       </c>
       <c r="B24" t="n">
-        <v>91841</v>
+        <v>93233</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,21 +2914,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2938,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490686</v>
+        <v>490304</v>
       </c>
       <c r="R24" t="n">
-        <v>7048041</v>
+        <v>7048251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,14 +3004,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128845752</v>
+        <v>128845782</v>
       </c>
       <c r="B25" t="n">
-        <v>92861</v>
+        <v>93233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3057,10 +3039,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490304</v>
+        <v>490634</v>
       </c>
       <c r="R25" t="n">
-        <v>7048251</v>
+        <v>7047955</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,45 +3105,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128845757</v>
+        <v>128845760</v>
       </c>
       <c r="B26" t="n">
-        <v>92819</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490551</v>
+        <v>490651</v>
       </c>
       <c r="R26" t="n">
-        <v>7047983</v>
+        <v>7048287</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,10 +3214,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128845770</v>
+        <v>128845747</v>
       </c>
       <c r="B27" t="n">
-        <v>92859</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3235,34 +3225,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1968</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490317</v>
+        <v>490412</v>
       </c>
       <c r="R27" t="n">
-        <v>7048250</v>
+        <v>7048136</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3325,10 +3323,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128845753</v>
+        <v>128845758</v>
       </c>
       <c r="B28" t="n">
-        <v>91539</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3336,34 +3334,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490409</v>
+        <v>490634</v>
       </c>
       <c r="R28" t="n">
-        <v>7048125</v>
+        <v>7047978</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3426,10 +3432,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128845780</v>
+        <v>128845761</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3469,10 +3475,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490313</v>
+        <v>490666</v>
       </c>
       <c r="R29" t="n">
-        <v>7048263</v>
+        <v>7048312</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,45 +3541,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128845765</v>
+        <v>128845780</v>
       </c>
       <c r="B30" t="n">
-        <v>91078</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5747</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490278</v>
+        <v>490313</v>
       </c>
       <c r="R30" t="n">
-        <v>7048250</v>
+        <v>7048263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3636,10 +3650,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128845789</v>
+        <v>17133716</v>
       </c>
       <c r="B31" t="n">
-        <v>92859</v>
+        <v>106140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3647,34 +3661,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1968</v>
+        <v>221137</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Töjsan, Jmt</t>
+          <t>Knutbränna /2 km SV/, Töjsan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490532</v>
+        <v>490581</v>
       </c>
       <c r="R31" t="n">
-        <v>7048001</v>
+        <v>7047937</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,12 +3715,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>1993-07-11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>1993-07-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Trakt: 20F0a11, taxyta: S1430. 2x(5X10 m) Strand +grund lagun. Översvämmas vid högvatten. En bäver bor helt nära ytan.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3717,23 +3736,131 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Älvstrand</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erik Lundmark</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+          <t>Lars-Åke Bäckström, Nils Dahlberg, Lisbeth Berntsson, Eva Jonsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>17133712</v>
+      </c>
+      <c r="B32" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Knutbränna /2 km SV/, Töjsan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>490581</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7047937</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1993-07-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1993-07-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Trakt: 20F0a11, taxyta: S1430. 2x(5X10 m) Strand +grund lagun. Översvämmas vid högvatten. En bäver bor helt nära ytan.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Älvstrand</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström, Nils Dahlberg, Lisbeth Berntsson, Eva Jonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39928-2022 artfynd.xlsx
+++ b/artfynd/A 39928-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845792</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845772</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845746</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845750</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845753</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845766</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845756</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17133733</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845748</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845770</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845775</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2092,6 +2162,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845789</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845774</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845781</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2395,6 +2480,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845791</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2496,6 +2586,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845757</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2692,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845754</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2698,6 +2798,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845769</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2799,6 +2904,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845765</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2900,6 +3010,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845773</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3001,6 +3116,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845752</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3102,6 +3222,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845782</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3211,6 +3336,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845760</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3320,6 +3450,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845747</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3429,6 +3564,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845758</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3538,6 +3678,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845761</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3647,6 +3792,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128845780</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3754,6 +3904,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17133716</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3861,8 +4016,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17133712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>